--- a/AI_Logs/AILog_NguyenTriThien_QE200082.xlsx
+++ b/AI_Logs/AILog_NguyenTriThien_QE200082.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUF\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TUF\OneDrive\Documents\GitHub\Social-Network-Friend-Suggestion-Project\AI_Logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B2A870-02C8-407D-B4F1-718D837776CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FF53B1-CC43-4830-8700-0BFFB88023B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -846,21 +846,21 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1178,14 +1178,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -1409,36 +1409,36 @@
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
-    <col min="7" max="7" width="81.77734375" customWidth="1"/>
-    <col min="8" max="8" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" customWidth="1"/>
+    <col min="5" max="5" width="30.77734375" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="54.44140625" customWidth="1"/>
+    <col min="8" max="8" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
@@ -1466,7 +1466,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>39</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="9" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" s="9" customFormat="1" ht="82.8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>111</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="9" customFormat="1" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" s="9" customFormat="1" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>117</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="9" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="9" customFormat="1" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>124</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>130</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>136</v>
       </c>
@@ -1829,7 +1829,7 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" customWidth="1"/>
     <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
@@ -1838,24 +1838,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -2175,20 +2175,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="4" spans="1:4" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
